--- a/data_extactor/batch_10_fa/batch_0010_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0010_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Online Merchants (تاجران آنلاین)</t>
+          <t>تاجران آنلاین (Online Merchants)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Online Services Manager</t>
+          <t>مدیر خدمات برخط</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AJAX | Adobe Dreamweaver | Adobe Photoshop | Apache Solr | Apache Struts | Apple macOS | Bing Ads | Bing for Power BI | نرم‌افزار وبلاگ‌نویسی | C# | CCBill | سیستم‌های مدیریت محتوا CMS | Drupal | Dynamic hypertext markup language DHTML | Enterprise JavaBeans | Extensible hypertext markup language XHTML | Extensible markup language XML | Facebook | نرم‌افزار حسابداری مالی | Google Ads | Google Analytics | Google Checkout | Hypertext markup language HTML | IBM Digital Analytics | IBM Domino | IBM InfoSphere DataStage | IBM WebSphere | Intuit QuickBooks | Intuit QuickBoooks Payments | نرم‌افزار ردیابی موجودی | JamBoard | JavaScript | LAMP Stack | Linux | Magento Analytics | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | نرم‌افزار اپلیکیشن موبایل | MyCommerce RegNow | MySQL | NetSuite ERP | Oracle Java | Oracle JavaServer Pages JSP | PHP | PayPal | PayPal Zettle | نرم‌افزار پردازش پرداخت ProPay | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Screencast-O-Matic | نرم‌افزار بازاریابی موتور جستجو SEM | نرم‌افزار بهینه‌سازی موتور جستجو SEO | نرم‌افزار صفحات نتایج موتور جستجو SERP | نرم‌افزار پردازش حمل و نقل | نرم‌افزار Shopify | Snorasson Holdings CCNow | Square | Structured query language SQL | نرم‌افزار مالیاتی | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار Webtrends | WordPress | YouTube | نرم‌افزار چک الکترونیکی | jQuery</t>
+          <t>AJAX | Adobe Dreamweaver | Adobe Photoshop | Apache Solr | Apache Struts | Apple macOS | Bing Ads | Bing for Power BI | نرم‌افزار وبلاگ‌نویسی | C# | CCBill | سیستم‌های مدیریت محتوا CMS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Enterprise JavaBeans | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | نرم‌افزار حسابداری مالی | Google Ads | Google Analytics | Google Checkout | زبان نشانه‌گذاری ابرمتن HTML | IBM Digital Analytics | IBM Domino | IBM InfoSphere DataStage | IBM WebSphere | Intuit QuickBooks | Intuit QuickBoooks Payments | نرم‌افزار ردیابی موجودی | JamBoard | JavaScript | LAMP Stack | Linux | Magento Analytics | Microsoft .NET Framework | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | نرم‌افزار اپلیکیشن موبایل | MyCommerce RegNow | MySQL | NetSuite ERP | Oracle Java | Oracle JavaServer Pages JSP | PHP | PayPal | PayPal Zettle | نرم‌افزار پردازش پرداخت ProPay | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Screencast-O-Matic | نرم‌افزار بازاریابی موتور جستجو SEM | نرم‌افزار بهینه‌سازی موتور جستجو SEO | نرم‌افزار صفحات نتایج موتور جستجو SERP | نرم‌افزار پردازش حمل و نقل | نرم‌افزار Shopify | Snorasson Holdings CCNow | Square | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مالیاتی | Twitter | نرم‌افزار مرورگر وب | نرم‌افزار Webtrends | WordPress | YouTube | نرم‌افزار چک الکترونیکی | jQuery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | نوشتن | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | فروش و بازاریابی | خدمات مشتری و شخصی | ارتباطات و رسانه | مدیریت و اداره | کامپیوتر و الکترونیک | اداری | ریاضیات | اقتصاد و حسابداری | تولید و پردازش</t>
+          <t>زبان انگلیسی | فروش و بازاریابی | خدمات مشتری و شخصی | ارتباطات و رسانه | مدیریت و اداره | رایانه و الکترونیک | اداری | ریاضیات | اقتصاد و حسابداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | حساسیت به مسئله | بیان نوشتاری | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال قیاسی | درک شفاهی | استدلال استقرایی | سازماندهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی</t>
+          <t>درک کتبی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | درک شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | تکرار تصمیم‌گیری | سر و کار داشتن با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | کارمندان کارگزاری | تحلیلگران هوش تجاری | کارمندان پیشخوان و اجاره | نمایندگان خدمات مشتری | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | کارمندان سفارشات | مأموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | استراتژیست‌های بازاریابی جستجو | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و ترویج | کارمندان کارگزاری | تحلیلگران هوش تجاری | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | کارمندان ثبت سفارش | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | استراتژیست‌های بازاریابی جستجو | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Security Management Specialists (متخصصان مدیریت امنیت)</t>
+          <t>متخصصان مدیریت امنیت (Security Management Specialists)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Physical Security Engineer | Physical Security Specialist | Security Advisor | Security Analyst | Security Consultant | Security Management Consultant | Security Specialist | Security and Workplace Violence Consultant</t>
+          <t>مهندس امنیت فیزیکی | کارشناس امنیت فیزیکی | مشاور امنیتی | تحلیل‌گر امنیت | مشاور امنیت | مشاور مدیریت امنیت | کارشناس امنیت | مشاور امنیت و خشونت در محل کار</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Amazon Web Services AWS | ArcSight Enterprise Threat and Risk Management | Chinotec Technologies Paros | Cisco Systems CiscoWorks | Customer information control system CICS | CyberArk | نرم‌افزار پایگاه داده | نرم‌افزار فایروال | نرم‌افزار IBM Tivoli | سیستم پیشگیری از نفوذ IPS | JavaScript | Kismet | Linux | نرم‌افزار MITRE ATT&amp;CK | سیستم‌های اطلاعات مدیریت MIS | McAfee | Metasploit | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار خدمات دایرکتوری شبکه | Nmap | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Java | نرم‌افزار ویرایش عکس | نرم‌افزار مدیریت دسترسی فیزیکی | SAP Crystal Reports | نرم‌افزار SAP | نرم‌افزار دروازه وب امن | Security assertion markup language SAML | ServiceNow | Single sign-on SSO | نرم‌افزار شبکه‌های اجتماعی | Splunk Enterprise | Structured query language SQL | Symantec PGP | Tenable Nessus | TrueCrypt | UNIX | نرم‌افزار کنفرانس ویدئویی | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار Amazon Web Services AWS | ArcSight Enterprise Threat and Risk Management | Chinotec Technologies Paros | Cisco Systems CiscoWorks | سیستم کنترل اطلاعات مشتری CICS | CyberArk | نرم‌افزار پایگاه داده | نرم‌افزار فایروال | نرم‌افزار IBM Tivoli | سیستم پیشگیری از نفوذ IPS | JavaScript | Kismet | Linux | نرم‌افزار MITRE ATT&amp;CK | سیستم‌های اطلاعات مدیریت MIS | McAfee | Metasploit | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | نرم‌افزار خدمات دایرکتوری شبکه | Nmap | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Java | نرم‌افزار ویرایش عکس | نرم‌افزار مدیریت دسترسی فیزیکی | SAP Crystal Reports | نرم‌افزار SAP | نرم‌افزار دروازه وب امن | زبان نشانه‌گذاری تایید امنیت SAML | ServiceNow | ورود یکباره SSO | نرم‌افزار شبکه‌های اجتماعی | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | Symantec PGP | Tenable Nessus | TrueCrypt | UNIX | نرم‌افزار ویدئوکنفرانس | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | صحبت کردن | درک مطلب | نوشتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | مدیریت و اداره | قانون و دولت | پرسنل و منابع انسانی | آموزش و پرورش | مهندسی و فناوری | روانشناسی | طراحی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | پرسنل و منابع انسانی | آموزش و پرورش | مهندسی و فناوری | روان‌شناسی | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک نوشتاری | بیان نوشتاری | استدلال استقرایی | سازماندهی اطلاعات | دید نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | خلاقیت | تشخیص گفتار | توجه انتخابی | دید دور | تجسم | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | تشخیص گفتار | توجه انتخابی | بینایی دور | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | فشار زمانی | تکرار تصمیم‌گیری | سلامت و ایمنی سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران انطباق | تحلیلگران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های کامپیوتری و اطلاعاتی | بازرسان ساخت و ساز و ساختمان | تحلیلگران پزشکی قانونی دیجیتال | مدیران مدیریت بحران | مهندسان پیشگیری و حفاظت از آتش | سرپرستان خط اول کارکنان امنیتی | افسران نظارت بر قمار و بازرسان قمار | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | تحلیلگران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | متخصصان پیشگیری از زیان خرده‌فروشی | مدیران امنیتی | نصابان سیستم‌های هشدار امنیتی و آتش‌نشانی</t>
+          <t>مدیران انطباق | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | بازرسان ساختمان و ساخت‌وساز | تحلیل‌گران جرم‌شناسی دیجیتال | مدیران مدیریت بحران | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان خط اول کارکنان امنیتی | ماموران نظارت بر قمار و بازرسان قمار | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | تحلیل‌گران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان پیشگیری از خسارت خرده‌فروشی | مدیران امنیتی | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accountants and Auditors (حسابداران و حسابرسان)</t>
+          <t>حسابداران و حسابرسان (Accountants and Auditors)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accountant | Accounting Officer | Audit Partner | Auditor | Certified Public Accountant (CPA) | Cost Accountant | Financial Auditor | General Accountant | Internal Auditor | Revenue Tax Specialist</t>
+          <t>حسابدار | مسئول حسابداری | شریک مؤسسه حسابرسی | حسابرس | حسابدار رسمی (CPA) | حسابدار صنعتی | حسابرس مالی | حسابدار عمومی | حسابرس داخلی | کارشناس درآمد مالیاتی</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1099 ProsSoftware | ACCUCert | ACL Audit Exchange | ACL Business Assurance Analytics | ADP Super Report Writer | ADP Workforce Now | ATX Total Accounting Office | ATX Total Engagement Office | ATX Total Tax Office | Abacus Tax | Accountants Templates JAZZ-It! | نرم‌افزار انطباق حسابداری | نرم‌افزار تشخیص تقلب حسابداری | نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | Accurate NXG | AcornSystems Corporate Performance Management | AcorynSystems Activity Based Costing/Management ABC/M | AdaptaSoft CyberPay | Adobe Acrobat | Advanced Micro Systems 1099-Etc | نرم‌افزار Alteryx | American Riviera Magtax | Apache Solr | Arbutus Analyzer | نرم‌افزار مدیریت دارایی | نرم‌افزار مدیریت حسابرسی | نرم‌افزار محیط برنامه‌ریزی و کنترل حسابرسی | AuditWare CaseWare Examiner | نرم‌افزار گزارش‌دهی مالی و حسابرسی AuditWare | نرم‌افزار تشخیص تقلب حسابرسان خودکار | Automation Counselors municiPAL | Avalara AvaTax ST | BNA Corporate Tax Audit Analyzer | BNA Estate and Gift Tax Suite | BNA Income Tax Planning Solutions | BNA Sales and Use Tax Rates and Forms | Best MIP Fund Accounting | Best Software CPAPayroll | Bi3 Audit Intelligence | Bi3 Financial Statement Fraud Analysis | نرم‌افزار صورت‌حساب | BizBench | Blackbaud The Raiser's Edge | Brentmark Estate Planning Quickview | CCH ProSystem fx TAX | CCIS AccountAbility | CPSI EHR System | CYMA IV Accounting for Windows | Cammack Computations Inter-Est | Cartesis ES Magnitude | Cartesis Magnitude iAnalysis | CaseWare International IDEA | CaseWare International IDEA SmartAnalyzer | CaseWare Working Papers | CashFlow Guardian | Cebos MQ1 Audit System | Choice Technologies PowerBill + | نرم‌افزار صورت‌حساب مشتری | Corel WordPerfect Office Suite | Corporate Responsibility System Technologies Limited Compliance Positioning System | نرم‌افزار حسابداری بهای تمام‌شده | Creative Solutions UltraTax 1040 | D'Arcangelo Galileo | نرم‌افزار ورود داده | نرم‌افزار استخراج داده | نرم‌افزار پایگاه داده | Datavantage | Delphi Technology | تست‌های تحلیل دیجیتال و آمار DATAS برای Excel | تست‌های تحلیل دیجیتال و آمار DATAS برای SAS | نرم‌افزار سیستم مدیریت اسناد | Eko | Epic Systems | نرم‌افزار برنامه‌ریزی املاک | Evron Computer Systems SAGE PFW (Platinum For Windows) | Exact Software Macola ES | FRx Software Microsoft FRx | FileMaker Pro | Financial Competence | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار صورت‌های مالی | نرم‌افزار استهلاک دارایی‌های ثابت | نرم‌افزار حسابداری صندوق | نرم‌افزار دفتر کل | Google Docs | Google Sheets | Google Slides | Guidance Software EnCase Enterprise | H&amp;R Block Tax | Healthcare common procedure coding system HCPCS | Heron CrossTie General Ledger | نرم‌افزار مدیریت منابع انسانی HRMS | IAD Audit Leverage | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IDMS Account Ability | نرم‌افزار تهیه اظهارنامه مالیات بر درآمد | InformationActive ActiveData for Excel | Intellitax financial solutions software | نرم‌افزار حسابرسی داخلی | Intrax ProcedureNet | Intuit Lacerte | Intuit ProSeries | Intuit QuickBooks | Intuit TurboTax | نرم‌افزار فاکتور | Iron Mountain Accutrac records management software | KPB Associates TaxStream | Kirix ProffiPoint | Lawson ERP | Lead Activity Analyzer | Lead Business Analyzer | LexisNexis | Lumigent Entegra | نرم‌افزار MEDITECH | MRO Audit Tracker | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MethodWare ProAudit Advisor | Micronetics Xpert Write-up | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics NAV | Microsoft Dynamics SL | Microsoft Excel | Microsoft Exchange | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Microsoft Works | Multiview Accounts Receivable | NetSuite ERP | New Millennium Communications Genesis Accounting | NewPortWave Year End Solutions | نرم‌افزار امنیت سایبری NortonLifeLock | OSI TrustWise | OmniRIM Records Management Suite | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | PROPHIX Enterprise | Paisley AutoAudit | Paisley Cardmap | Paisley Focus Control Assurance | Paisley IssueTrack | Paisley RiskNavigator | Palisade @Risk | نرم‌افزار حقوق و دستمزد | Pentana audit work system PAWS | Pleier Audit Management System | نرم‌افزار مدیریت تمرین PMS | PricewaterhouseCoopers TeamMate | Pro Systems Client Write-Up System for Windows | Profit Developers Electronic File Interchange | Qlik Tech QlikView | R | RSM McGladrey Advanced Practice Solutions Paperless Audit | RSM McGladrey Auditor Assistant | نرم‌افزار حسابرسی بازیابی | Roundtable Software Advantage Accounting System | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 300 Construction and Real Estate | Sage 50 Accounting | Sage BusinessWorks | Sage CPAAccounts Payable | Sage CPAAccounts Receivable | Sage CPAClient Checkbook | Sage CPADocument Manager | Sage EDP Payroll Tax | Sage ERP Accpac | Sage HRMS | Sage HandiSoft HandiLedger | Sage MAS 200 ERP | Sage MAS 500 | Sage Platinum for Windows PFW | Sageworks ProfitCents | نرم‌افزار Salesforce | Sampson Data Pattern Index software | Softrax Revenue Management | Solutions Technology &amp; Software HR Premier | Star Software Fixed Asset Depreciation | Star Software Materiality Calculator | Structured query language SQL | Summit Software Summit Biofuels Accounting | Swift | Sync Essentials Trade Accountant | Tableau | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | TechSmith Camtasia | Teradata Database | Thomson Creative Solutions Engagement CS | Thomson Creative Solutions Financial Analysis CS | Thomson GoSystem Tax | Thomson PPC e-Tools Suite | Thomson Reuters Risk Management | نرم‌افزار TimeValue | TopCAATs | TrendTracker Compliance Solution | نرم‌افزار غرامت کارگران Tropics | Tumbleweed SecureTransport | UA Business Software Professional Edition | UNIX | Universal Tax Systems TaxWise | WizSoft WizRule | WizSoft WizWhy | WorkForce Software EmpCenter Time and Attendance | نرم‌افزار Workday | Yardi Systems Yardi Enterprise | نرم‌افزار Yardi | eXtensible Business Reporting Language XBRL</t>
+          <t>1099 ProsSoftware | ACCUCert | ACL Audit Exchange | ACL Business Assurance Analytics | ADP Super Report Writer | ADP Workforce Now | ATX Total Accounting Office | ATX Total Engagement Office | ATX Total Tax Office | Abacus Tax | Accountants Templates JAZZ-It! | نرم‌افزار انطباق حسابداری | نرم‌افزار تشخیص تقلب حسابداری | نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | Accurate NXG | AcornSystems Corporate Performance Management | AcorynSystems Activity Based Costing/Management ABC/M | AdaptaSoft CyberPay | Adobe Acrobat | Advanced Micro Systems 1099-Etc | نرم‌افزار Alteryx | American Riviera Magtax | Apache Solr | Arbutus Analyzer | نرم‌افزار مدیریت دارایی | نرم‌افزار مدیریت حسابرسی | نرم‌افزار محیط برنامه‌ریزی و کنترل حسابرسی | AuditWare CaseWare Examiner | نرم‌افزار گزارش‌دهی مالی و حسابرسی AuditWare | نرم‌افزار تشخیص تقلب حسابرسان خودکار | Automation Counselors municiPAL | Avalara AvaTax ST | BNA Corporate Tax Audit Analyzer | BNA Estate and Gift Tax Suite | BNA Income Tax Planning Solutions | BNA Sales and Use Tax Rates and Forms | Best MIP Fund Accounting | Best Software CPAPayroll | Bi3 Audit Intelligence | Bi3 Financial Statement Fraud Analysis | نرم‌افزار صدور صورتحساب | BizBench | Blackbaud The Raiser's Edge | Brentmark Estate Planning Quickview | CCH ProSystem fx TAX | CCIS AccountAbility | CPSI EHR System | CYMA IV Accounting for Windows | Cammack Computations Inter-Est | Cartesis ES Magnitude | Cartesis Magnitude iAnalysis | CaseWare International IDEA | CaseWare International IDEA SmartAnalyzer | CaseWare Working Papers | CashFlow Guardian | Cebos MQ1 Audit System | Choice Technologies PowerBill + | نرم‌افزار صورت‌حساب مشتری | Corel WordPerfect Office Suite | Corporate Responsibility System Technologies Limited Compliance Positioning System | نرم‌افزار حسابداری هزینه | Creative Solutions UltraTax 1040 | D'Arcangelo Galileo | نرم‌افزار ورود داده | نرم‌افزار استخراج داده | نرم‌افزار پایگاه داده | Datavantage | Delphi Technology | تست‌های تحلیل دیجیتال و آمار DATAS برای Excel | تست‌های تحلیل دیجیتال و آمار DATAS برای SAS | نرم‌افزار سیستم مدیریت اسناد | Eko | Epic Systems | نرم‌افزار برنامه‌ریزی املاک | Evron Computer Systems SAGE PFW (Platinum For Windows) | Exact Software Macola ES | FRx Software Microsoft FRx | FileMaker Pro | Financial Competence | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار صورت‌های مالی | نرم‌افزار استهلاک دارایی‌های ثابت | نرم‌افزار حسابداری صندوق | نرم‌افزار دفتر کل | Google Docs | Google Sheets | Google Slides | Guidance Software EnCase Enterprise | H&amp;R Block Tax | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Heron CrossTie General Ledger | نرم‌افزار مدیریت منابع انسانی HRMS | IAD Audit Leverage | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IDMS Account Ability | نرم‌افزار تهیه اظهارنامه مالیات بر درآمد | InformationActive ActiveData for Excel | Intellitax financial solutions software | نرم‌افزار حسابرسی داخلی | Intrax ProcedureNet | Intuit Lacerte | Intuit ProSeries | Intuit QuickBooks | Intuit TurboTax | نرم‌افزار فاکتور | Iron Mountain Accutrac records management software | KPB Associates TaxStream | Kirix ProffiPoint | Lawson ERP | Lead Activity Analyzer | Lead Business Analyzer | LexisNexis | Lumigent Entegra | نرم‌افزار MEDITECH | MRO Audit Tracker | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MethodWare ProAudit Advisor | Micronetics Xpert Write-up | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics NAV | Microsoft Dynamics SL | Microsoft Excel | Microsoft Exchange | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Windows | Microsoft Word | Microsoft Works | Multiview Accounts Receivable | NetSuite ERP | New Millennium Communications Genesis Accounting | NewPortWave Year End Solutions | نرم‌افزار امنیت سایبری NortonLifeLock | OSI TrustWise | OmniRIM Records Management Suite | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | PROPHIX Enterprise | Paisley AutoAudit | Paisley Cardmap | Paisley Focus Control Assurance | Paisley IssueTrack | Paisley RiskNavigator | Palisade @Risk | نرم‌افزار حقوق و دستمزد | Pentana audit work system PAWS | Pleier Audit Management System | نرم‌افزار مدیریت مطب PMS | PricewaterhouseCoopers TeamMate | Pro Systems Client Write-Up System for Windows | Profit Developers Electronic File Interchange | Qlik Tech QlikView | R | RSM McGladrey Advanced Practice Solutions Paperless Audit | RSM McGladrey Auditor Assistant | نرم‌افزار حسابرسی بازیابی | Roundtable Software Advantage Accounting System | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 300 Construction and Real Estate | Sage 50 Accounting | Sage BusinessWorks | Sage CPAAccounts Payable | Sage CPAAccounts Receivable | Sage CPAClient Checkbook | Sage CPADocument Manager | Sage EDP Payroll Tax | Sage ERP Accpac | Sage HRMS | Sage HandiSoft HandiLedger | Sage MAS 200 ERP | Sage MAS 500 | Sage Platinum for Windows PFW | Sageworks ProfitCents | نرم‌افزار Salesforce | Sampson Data Pattern Index software | Softrax Revenue Management | Solutions Technology &amp; Software HR Premier | Star Software Fixed Asset Depreciation | Star Software Materiality Calculator | زبان پرس‌وجوی ساختاریافته SQL | Summit Software Summit Biofuels Accounting | Swift | Sync Essentials Trade Accountant | Tableau | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | TechSmith Camtasia | Teradata Database | Thomson Creative Solutions Engagement CS | Thomson Creative Solutions Financial Analysis CS | Thomson GoSystem Tax | Thomson PPC e-Tools Suite | Thomson Reuters Risk Management | نرم‌افزار TimeValue | TopCAATs | TrendTracker Compliance Solution | نرم‌افزار غرامت کارگران Tropics | Tumbleweed SecureTransport | UA Business Software Professional Edition | UNIX | Universal Tax Systems TaxWise | WizSoft WizRule | WizSoft WizWhy | WorkForce Software EmpCenter Time and Attendance | نرم‌افزار Workday | Yardi Systems Yardi Enterprise | نرم‌افزار Yardi | eXtensible Business Reporting Language XBRL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | نوشتن | نظارت | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | اداری | کامپیوتر و الکترونیک</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال استقرایی | دید نزدیک | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | سازماندهی اطلاعات | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تکرار تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف مشابه | سر و کار داشتن با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان صورت‌حساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران بودجه | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان خط اول کارکنان اداری و پشتیبانی اداری | تحلیلگران مدیریت | کارمندان حقوق و دستمزد و زمان‌سنجی | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | دستیاران آماری | بازرسان و جمع‌آوری‌کنندگان مالیات و مأموران درآمد | تهیه‌کنندگان مالیات | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران بودجه | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | تحلیل‌گران مدیریت | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | دستیاران آماری | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Appraisers of Personal and Business Property (ارزیابان اموال شخصی و تجاری)</t>
+          <t>ارزیابان اموال شخصی و تجاری (Appraisers of Personal and Business Property)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Accredited Appraiser | Aircraft Appraiser | Appraiser | Art Appraiser | Certified Appraiser | Gem and Jewelry Appraiser | Jewelry Appraiser | Personal Property Appraiser</t>
+          <t>ارزیاب دارای گواهی صلاحیت | ارزیاب هواپیما | ارزیاب | ارزیاب آثار هنری | ارزیاب دارای گواهی صلاحیت | ارزیاب سنگ‌های قیمتی و جواهر | ارزیاب جواهر | ارزیاب اموال شخصی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نوشتن | گوش دادن فعال | صحبت کردن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اداری | مدیریت و اداره | کامپیوتر و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | درک نوشتاری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | دید دور | تشخیص رنگ بصری | توجه انتخابی</t>
+          <t>درک شفاهی | بینایی نزدیک | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | بینایی دور | تشخیص رنگ بصری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | سر و کار داشتن با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل محیطی</t>
+          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | ارزیابان و ممیزان املاک | کارمندان کارگزاری | برآوردکنندگان هزینه | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | بازرسان و بازپرسان اموال دولتی | ارزیابان بیمه، خسارت خودرو | بیمه‌گران | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان تدارکات | مدیران اموال، املاک و انجمن‌های اجتماعی | مأموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | دلالان املاک | نمایندگان فروش املاک | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و جمع‌آوری‌کنندگان مالیات و مأموران درآمد | بازرسان عنوان، چک‌کنندگان و جستجوگران | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>حسابداران و حسابرسان | ارزیابان و ممیزان املاک | کارمندان کارگزاری | برآوردکنندگان هزینه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | بازرسان و محققان اموال دولتی | ارزیابان بیمه، خسارت خودرو | بیمه‌گران | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان تدارکات | مدیران املاک، مستغلات و انجمن‌های اجتماعی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | کارگزاران املاک | نمایندگان فروش املاک | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Appraisers and Assessors of Real Estate (ارزیابان و ممیزان املاک)</t>
+          <t>ارزیابان و ممیزان املاک (Appraisers and Assessors of Real Estate)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Appraiser | Assessor | Certified Real Estate Appraiser | Certified Residential Appraiser | Commercial Appraiser | County Assessor | Field Appraiser | Real Estate Appraiser | Real Property Appraiser | Tax Assessor</t>
+          <t>ارزیاب | ارزیاب | ارزیاب املاک دارای گواهی صلاحیت | ارزیاب املاک مسکونی دارای گواهی صلاحیت | ارزیاب املاک تجاری | ارزیاب املاک شهرستان | ارزیاب میدانی | ارزیاب املاک | ارزیاب اموال غیرمنقول | ارزیاب مالیاتی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ACI Appraiser's Choice | Apex IV Assessor | Apex IV Fee Appraiser | Apex MobileSketch | Apple iOS | Ascend Property Assessment | Bradford ClickFORMS | Bruno Realty eNeighboorhoods | Business Management Systems Municipal Geographic Management System MGMS | CPR International GeneralCOST Estimator | CPR Visual Estimator | Compass Municipal Services CAMAlot | نرم‌افزار ارزیابی انبوه به کمک کامپیوتر CAMA | Concierge Systems Report Concierge | Construction Management Software ProEst | نرم‌افزار برآورد هزینه | نرم‌افزار پایگاه داده | Emerald Data Deed-Chek | FBS Data Systems Flexmls | GCS Property Assessment and Tax Billing | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی مکانیکی زمین GDA | Google Meet | نرم‌افزار Google Workspace | Govern Software GovMap | Govern Software Land and Permits Management System | Greenbrier Graphics Deed Plotter | HP 49G+ Appraiser Fee Calculator | Hansen CAMA | Howard and Friends Computer CMA Plus | Informatik MapDraw Deed Mapper | Manatron CustomCAMA | Manatron MVP Tax | Manatron ProVal Plus | Manufacturing Technology Costimater | سیستم سوابق ارزیابی انبوه MARS | MicroSolve CAMA | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Modellium PariTOP | نرم‌افزار لیست چندگانه | نرم‌افزار جستجوی عنوان آنلاین و گزارش ملک | REI Wise Commercial | RPIS Silent CMA | Real Edge | Real Estate Center Caparate Calculator | RealData Comparative Lease Analysis | Realty Tools Toolkit for Market Share | Softree Technical Systems Terrain Tools | TietoEnator ProMatch | ValueTech Report Builder | Visual PAMSPro | نرم‌افزار مرورگر وب | Wilson's Computer Applications RealEasy Appraisals | Wilson's Computer Applications RealEasy Photos Plus | WinEstimator WinEst | WinGap | نرم‌افزار Yardi | a la mode Pocket TOTAL | a la mode WinTOTAL | eTrac</t>
+          <t>ACI Appraiser's Choice | Apex IV Assessor | Apex IV Fee Appraiser | Apex MobileSketch | Apple iOS | Ascend Property Assessment | Bradford ClickFORMS | Bruno Realty eNeighboorhoods | Business Management Systems Municipal Geographic Management System MGMS | CPR International GeneralCOST Estimator | CPR Visual Estimator | Compass Municipal Services CAMAlot | نرم‌افزار ارزیابی انبوه به کمک کامپیوتر CAMA | Concierge Systems Report Concierge | نرم‌افزار مدیریت ساخت ProEst | نرم‌افزار برآورد هزینه | نرم‌افزار پایگاه داده | Emerald Data Deed-Chek | FBS Data Systems Flexmls | GCS Property Assessment and Tax Billing | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Google Meet | نرم‌افزار Google Workspace | Govern Software GovMap | Govern Software Land and Permits Management System | Greenbrier Graphics Deed Plotter | HP 49G+ Appraiser Fee Calculator | Hansen CAMA | Howard and Friends Computer CMA Plus | Informatik MapDraw Deed Mapper | Manatron CustomCAMA | Manatron MVP Tax | Manatron ProVal Plus | Manufacturing Technology Costimater | سیستم سوابق ارزیابی انبوه MARS | MicroSolve CAMA | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Modellium PariTOP | نرم‌افزار لیست چندگانه | نرم‌افزار جستجوی عنوان آنلاین و گزارش ملک | REI Wise Commercial | RPIS Silent CMA | Real Edge | Real Estate Center Caparate Calculator | RealData Comparative Lease Analysis | Realty Tools Toolkit for Market Share | Softree Technical Systems Terrain Tools | TietoEnator ProMatch | ValueTech Report Builder | Visual PAMSPro | نرم‌افزار مرورگر وب | Wilson's Computer Applications RealEasy Appraisals | Wilson's Computer Applications RealEasy Photos Plus | WinEstimator WinEst | WinGap | نرم‌افزار Yardi | a la mode Pocket TOTAL | a la mode WinTOTAL | eTrac</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نوشتن | صحبت کردن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ریاضیات | ساختمان و ساخت و ساز | خدمات مشتری و شخصی | اقتصاد و حسابداری | کامپیوتر و الکترونیک | مدیریت و اداره | قانون و دولت | جغرافیا</t>
+          <t>زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص گفتار | درک شفاهی | وضوح گفتار | بیان شفاهی | درک نوشتاری | استدلال استقرایی | استدلال قیاسی | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | دید دور | توانایی عددی | سازماندهی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
+          <t>بینایی نزدیک | تشخیص گفتار | درک شفاهی | وضوح گفتار | بیان شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توانایی عددی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | در وسیله نقلیه محصور یا کار با تجهیزات محصور | نامه‌ها و یادداشت‌های کتبی | بحث‌های رودررو با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | تماس با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای کنترل محیطی | تکرار تصمیم‌گیری</t>
+          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا درست بودن | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نامه‌ها و یادداشت‌های کتبی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | ارزیابان اموال شخصی و تجاری | بازرسان ساخت و ساز و ساختمان | برآوردکنندگان هزینه | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | تحلیلگران مالی و سرمایه‌گذاری | بازرسان و بازپرسان اموال دولتی | ارزیابان بیمه، خسارت خودرو | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مدیران اموال، املاک و انجمن‌های اجتماعی | مأموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | دلالان املاک | نمایندگان فروش املاک | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | نقشه‌برداران | بازرسان و جمع‌آوری‌کنندگان مالیات و مأموران درآمد | تهیه‌کنندگان مالیات | بازرسان عنوان، چک‌کنندگان و جستجوگران</t>
+          <t>حسابداران و حسابرسان | ارزیابان اموال شخصی و تجاری | بازرسان ساختمان و ساخت‌وساز | برآوردکنندگان هزینه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | تحلیلگران مالی و سرمایه‌گذاری | بازرسان و محققان اموال دولتی | ارزیابان بیمه، خسارت خودرو | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مدیران املاک، مستغلات و انجمن‌های اجتماعی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | کارگزاران املاک | نمایندگان فروش املاک | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | نقشه‌برداران | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Budget Analysts (تحلیلگران بودجه)</t>
+          <t>تحلیلگران بودجه (Budget Analysts)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Budget Analyst | Budget Coordinator | Budget Officer | Budget Planning Analyst | Budget and Policy Analyst | Cost Analyst | Financial Services Officer | Fiscal Analyst | Fiscal Budget Analyst</t>
+          <t>تحلیل‌گر بودجه | هماهنگ‌کننده بودجه | مسئول بودجه | تحلیل‌گر برنامه‌ریزی بودجه | تحلیل‌گر بودجه و سیاست‌گذاری | تحلیل‌گر هزینه | مسئول خدمات مالی | تحلیل‌گر مالی دولتی | تحلیل‌گر بودجه دولتی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adaptive Planning | سیستم‌های نظارت بر بودجه | نرم‌افزار بودجه‌بندی، پیش‌بینی و برنامه‌ریزی | Business Objects Data Integrator | نرم‌افزار مدیریت عملکرد کسب‌وکار BPM | Deltek Costpoint | نرم‌افزار ایمیل | Everest Software Advanced | Extensity MPC | FRx Software Microsoft Forecaster | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار حسابداری صندوق | نرم‌افزار گرافیکی | سیستم مدیریت منابع انسانی HRMS | Hyperion Enterprise | IBM Cognos Business Intelligence | IBM Cognos Planning | Lilly Software Associates VISUAL Enterprise | Microsoft Access | Microsoft Dynamics GP | Microsoft Excel | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | NetSuite NetERP | نرم‌افزار پردازش تحلیلی آنلاین OLAP | Open Systems TRAVERSE | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle PeopleSoft Enterprise | Oracle PeopleSoft Financials | Oracle Performance Management Suites | OutlookSoft | نرم‌افزار حقوق و دستمزد | نرم‌افزار پایگاه داده رابطه‌ای | Revelwood | SAP Business One | SAP BusinessObjects Crystal Reports | SAP Crystal Xcelsius | نرم‌افزار SAP | Sage Active Planner | Sage ERP Accpac | Sage MAS 200 ERP | Sage MAS 90 ERP | Satori Group proCube | نرم‌افزار آماری | Structured query language SQL | نرم‌افزار زمان و حضور | Ultimate Software UltiPro Workplace | Valiant Vantage</t>
+          <t>Adaptive Planning | سیستم‌های نظارت بر بودجه | نرم‌افزار بودجه‌بندی، پیش‌بینی و برنامه‌ریزی | Business Objects Data Integrator | نرم‌افزار مدیریت عملکرد کسب‌وکار BPM | Deltek Costpoint | نرم‌افزار ایمیل | Everest Software Advanced | Extensity MPC | FRx Software Microsoft Forecaster | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار حسابداری صندوق | نرم‌افزار گرافیکی | سیستم مدیریت منابع انسانی HRMS | Hyperion Enterprise | IBM Cognos Business Intelligence | IBM Cognos Planning | Lilly Software Associates VISUAL Enterprise | Microsoft Access | Microsoft Dynamics GP | Microsoft Excel | Microsoft FRx | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | NetSuite NetERP | نرم‌افزار پردازش تحلیلی آنلاین OLAP | Open Systems TRAVERSE | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle PeopleSoft Enterprise | Oracle PeopleSoft Financials | Oracle Performance Management Suites | OutlookSoft | نرم‌افزار حقوق و دستمزد | نرم‌افزار پایگاه داده رابطه‌ای | Revelwood | SAP Business One | SAP BusinessObjects Crystal Reports | SAP Crystal Xcelsius | نرم‌افزار SAP | Sage Active Planner | Sage ERP Accpac | Sage MAS 200 ERP | Sage MAS 90 ERP | Satori Group proCube | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار حضور و غیاب | Ultimate Software UltiPro Workplace | Valiant Vantage</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | صحبت کردن | یادگیری فعال | نوشتن | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری | کامپیوتر و الکترونیک | خدمات مشتری و شخصی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال ریاضی | توانایی عددی | حساسیت به مسئله | استدلال قیاسی | سازماندهی اطلاعات | وضوح گفتار | بیان نوشتاری | استدلال استقرایی | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | توانایی عددی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | بیان کتبی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت تکرار وظایف مشابه | اهمیت دقیق یا صحیح بودن | تکرار تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | نتایج کاری و خروجی‌های سایر کارکنان | محیط داخلی، دارای کنترل محیطی | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و حسابرسی | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مدیران جمع‌آوری کمک مالی | مدیران صندوق‌های سرمایه‌گذاری | تحلیلگران مدیریت | کارمندان حقوق و دستمزد و زمان‌سنجی | مشاوران مالی شخصی | متخصصان مدیریت پروژه | بازرسان و جمع‌آوری‌کنندگان مالیات و مأموران درآمد | تهیه‌کنندگان مالیات | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و حسابرسی | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مدیران جمع‌آوری کمک‌های مالی | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | متخصصان مدیریت پروژه | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit Analysts (تحلیلگران اعتبار)</t>
+          <t>تحلیلگران اعتبار (Credit Analysts)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Credit Administrator | Credit Analyst | Credit Officer | Credit Representative | Credit Risk Analyst | Credit and Collections Analyst | Municipal Fixed Income Analyst</t>
+          <t>مسئول امور اعتباری | تحلیل‌گر اعتباری | مسئول اعتبارات | نماینده اعتبار | تحلیل‌گر ریسک اعتباری | تحلیل‌گر اعتبارات و وصول مطالبات | تحلیل‌گر اوراق درآمد ثابت شهرداری</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CGI-AMS BureauLink Enterprise | CGI-AMS CACS Enterprise | CGI-AMS Strata | سیستم مدیریت اعتبار و وام‌دهی CALMS | نرم‌افزار تحلیل اعتبار و ریسک | نرم‌افزار تشخیص تقلب اعتبار | Dun and Bradstreet Global DecisionMaker | Equifax Advanced Decisioning | Equifax Application Engine | Equifax InterConnect | Experian Credinomics | Experian Detect | Experian FraudShield | Experian Quest | Experian Retention Triggers | Experian Strategy Management | Experian Transact SM | نرم‌افزار مدل ریسک کاربرد Fair Isaac | Fair Isaac Capstone Decision Manager | Fair Isaac Falcon ID | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Moody's KMV CreditEdge | Moody's KMV Decisions | Moody's KMV Financial Analyst | Moody's KMV Risk Advisor | Moody's KMV Risk Analyst | Oracle Business Intelligence Enterprise Edition | Oracle JD Edwards EnterpriseOne | Python | نرم‌افزار SAP | SAS | Structured query language SQL | eCredit Enterprise</t>
+          <t>CGI-AMS BureauLink Enterprise | CGI-AMS CACS Enterprise | CGI-AMS Strata | سیستم مدیریت اعتبار و وام‌دهی CALMS | نرم‌افزار تحلیل اعتبار و ریسک | نرم‌افزار تشخیص تقلب اعتبار | Dun and Bradstreet Global DecisionMaker | Equifax Advanced Decisioning | Equifax Application Engine | Equifax InterConnect | Experian Credinomics | Experian Detect | Experian FraudShield | Experian Quest | Experian Retention Triggers | Experian Strategy Management | Experian Transact SM | نرم‌افزار مدل ریسک کاربرد Fair Isaac | Fair Isaac Capstone Decision Manager | Fair Isaac Falcon ID | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Moody's KMV CreditEdge | Moody's KMV Decisions | Moody's KMV Financial Analyst | Moody's KMV Risk Advisor | Moody's KMV Risk Analyst | Oracle Business Intelligence Enterprise Edition | Oracle JD Edwards EnterpriseOne | Python | نرم‌افزار SAP | SAS | زبان پرس‌وجوی ساختاریافته SQL | eCredit Enterprise</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | صحبت کردن | گوش دادن فعال | ریاضیات | نوشتن | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | سخن گفتن | گوش دادن فعال | ریاضیات | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک نوشتاری | استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی عددی | دید نزدیک | سازماندهی اطلاعات | بیان نوشتاری | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>بیان شفاهی | درک کتبی | استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی عددی | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف مشابه | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تماس با دیگران | تکرار تصمیم‌گیری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | ارتباط با دیگران | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | جمع‌آوری‌کنندگان صورت‌حساب و حساب | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش ادعاها و سیاست‌های بیمه | بیمه‌گران | مدیران صندوق‌های سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و جمع‌آوری‌کنندگان مالیات و مأموران درآمد | تهیه‌کنندگان مالیات | تحویل‌داران</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | بیمه‌گران | مدیران صندوق سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial and Investment Analysts (تحلیلگران مالی و سرمایه‌گذاری)</t>
+          <t>تحلیلگران مالی و سرمایه‌گذاری (Financial and Investment Analysts)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Analyst | Credit Products Officer | Equity Research Analyst | Financial Analyst | Investment Analyst | Planning Analyst | Portfolio Manager | Real Estate Analyst | Securities Analyst | Trust Officer</t>
+          <t>تحلیل‌گر | مسئول محصولات اعتباری | تحلیل‌گر پژوهش سهام | تحلیل‌گر مالی | تحلیل‌گر سرمایه‌گذاری | تحلیل‌گر برنامه‌ریزی | مدیر پورتفوی | تحلیل‌گر املاک | تحلیل‌گر اوراق بهادار | مسئول امور امانی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | Advanced Portfolio Technologies Report Builder | Advanced Portfolio Technologies Simulator | نرم‌افزار Alteryx | Analyse-it | AnalyzerXL | نرم‌افزار تحلیل مستمری‌ها | Apache Hive | Apache Pig | Apple AppleWorks | Apple Keynote | نرم‌افزار تحلیل فنی Aspen Graphics | BizBench | BizPricer | Bloomberg Professional | Business Forecast Systems Forecast Pro | نرم‌افزار هوش تجاری | Corel QuattroPro | نرم‌افزار تجسم داده | DealMaven Comparable Company Valuation Analysis | DealMaven M&amp;A Accretion/Dilution One-Pager | DealMaven Modeling ToolPack for Excel | DealMaven PresLink for PowerPoint and Word | Decisioneering Crystal Ball | Delphi Technology | Derivatives Imagine Trading System | Derivicom FinOptions XL | نرم‌افزار پیش‌بینی اقتصادی | نرم‌افزار ایمیل | Experian Credinomics | Express Business Valuations | FileMaker Pro | FinEng Solutions PerfoRM | FinEng Solutions Quantis | نرم‌افزار مدل‌سازی مالی | نرم‌افزار تحلیل الگوی فراکتال | نرم‌افزار حسابداری صندوق | نرم‌افزار بهینه‌سازی الگوریتم ژنتیک | نرم‌افزار الگوریتم ژنتیک | Google Docs | Google Slides | Harland Financial Solutions DecisionPro | نرم‌افزار مدیریت منابع انسانی HRMS | I-flex Solutions Reveleus Investment Performance Measurement | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Lotus Approach | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Innova Financial Solutions Derivatives Expert | Intuit QuickBooks | Ivorix Neurostrategy Finance | Keypoint DataDesk | Leading Market Technologies EXPO | LexisNexis | Longview Consolidation | Longview Performance Management Platform | Longview Solutions Khalix | نرم‌افزار پیش‌بینی بازار | Marketo Marketing Automation | نرم‌افزار ریاضی | Matheny Pattern Forecaster Plus | MergerStat Control Premiums | MergerStat Price to Earnings Ratios | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | MoneySoft Corporate Valuation | نرم‌افزار شبیه‌سازی مونت کارلو | Montgomery Investment Technology Bonds XL | Montgomery Investment Technology Exotics XL | Montgomery Investment Technology FinTools | Montgomery Investment Technology Options XL | Montgomery Investment Technology QuoteTools | Montgomery Investment Technology Risk XL | Montgomery Investment Technology SigTools | Montgomery Investment Technology Utility XL | Moody's KMV CreditEdge | Moody's RiskCalc | Moss Adams Profit Mentor | نرم‌افزار تحلیل صندوق‌های سرمایه‌گذاری مشترک | NetSuite ERP | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions Trading Solutions | NeuroSolutions for MatLab | OptionVue Options Analysis | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Essbase | Oracle Fusion Applications | Oracle Hyperion | Oracle Hyperion Financial Management | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Palisade Bond @nalyst | Palisade Evolver | Palisade StatTools | نرم‌افزار تشخیص الگو | Peer-to-Peer Financial Analysis | نرم‌افزار Perforce Helix | Pi Blue OptWorks Excel | نرم‌افزار مدیریت پورتفولیو | نرم‌افزار قیمت‌گذاری | Qlik Tech QlikView | Quantifying marketability discount QMD modeling software | R | نرم‌افزار تولید گزارش | نرم‌افزار گزارش‌دهی | RiskMetrics Group WealthBench | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SSA Global Infinium Financial Management | Sage 50 Accounting | نرم‌افزار Salesforce | نرم‌افزار تحلیل اوراق بهادار | Spreadware Business Financial Analysis | Spreadware Business Valuator | Spreadware Pro Forma | StataCorp Stata | Steele Mutual Fund and Variable Annuity Expert | Structured query language SQL | SunGard BancWare | SunGard Kiodex Risk Workbench | Tableau | نرم‌افزار مالیاتی | TechHackers Convertible Bond @nalyst | TechHackers Credit @nalyst | TechHackers Exotic @nalyst | TechHackers Financial @nalyst | TechHackers IRO @nalyst | TechHackers MBS @nalyst | TechHackers Swap @nalyst | Teradata Database | Tetrahex Fractal Finance | The MathWorks MATLAB | TickQuest NeoTicker | Tips Standard Securities Calculation Bond Analytics Module | Tips Standard Securities Calculation Mortgage-Backed Analytics Module | TradeTools Financial Market Databases | TradeTools Monthly U.S. Economic Database | Trendsetter Software ProAnalyst | Unlimited Learning Resources Valusource Pro | ValuSource BIZCOMPS | Ward Systems Group GeneHunter | Ward Systems Group NeuralShell Predictor | Ward Systems Group NeuroShell Trader | نرم‌افزار مرورگر وب | Whitebirch Software Projected Financials | Wolfram Research Derivatives | Wolfram Research Mathematica | Wolfram Research Mathematica Finance Essentials | Wolfram Research Mathematica UnRisk Pricing Engine | نرم‌افزار Workday | نرم‌افزار Yardi | dailyVest Investment Personalization Platform</t>
+          <t>ADP Workforce Now | Advanced Portfolio Technologies Report Builder | Advanced Portfolio Technologies Simulator | نرم‌افزار Alteryx | Analyse-it | AnalyzerXL | نرم‌افزار تحلیل مستمری‌ها | Apache Hive | Apache Pig | Apple AppleWorks | Apple Keynote | نرم‌افزار تحلیل فنی Aspen Graphics | BizBench | BizPricer | Bloomberg Professional | Business Forecast Systems Forecast Pro | نرم‌افزار هوش تجاری | Corel QuattroPro | نرم‌افزار تجسم داده | DealMaven Comparable Company Valuation Analysis | DealMaven M&amp;A Accretion/Dilution One-Pager | DealMaven Modeling ToolPack for Excel | DealMaven PresLink for PowerPoint and Word | Decisioneering Crystal Ball | Delphi Technology | Derivatives Imagine Trading System | Derivicom FinOptions XL | نرم‌افزار پیش‌بینی اقتصادی | نرم‌افزار ایمیل | Experian Credinomics | Express Business Valuations | FileMaker Pro | FinEng Solutions PerfoRM | FinEng Solutions Quantis | نرم‌افزار مدل‌سازی مالی | نرم‌افزار تحلیل الگوی فراکتال | نرم‌افزار حسابداری صندوق | نرم‌افزار بهینه‌سازی الگوریتم ژنتیک | نرم‌افزار الگوریتم ژنتیک | Google Docs | Google Slides | Harland Financial Solutions DecisionPro | نرم‌افزار مدیریت منابع انسانی HRMS | I-flex Solutions Reveleus Investment Performance Measurement | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Lotus Approach | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Innova Financial Solutions Derivatives Expert | Intuit QuickBooks | Ivorix Neurostrategy Finance | Keypoint DataDesk | Leading Market Technologies EXPO | LexisNexis | Longview Consolidation | Longview Performance Management Platform | Longview Solutions Khalix | نرم‌افزار پیش‌بینی بازار | Marketo Marketing Automation | نرم‌افزار ریاضی | Matheny Pattern Forecaster Plus | MergerStat Control Premiums | MergerStat Price to Earnings Ratios | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | MoneySoft Corporate Valuation | نرم‌افزار شبیه‌سازی مونت کارلو | Montgomery Investment Technology Bonds XL | Montgomery Investment Technology Exotics XL | Montgomery Investment Technology FinTools | Montgomery Investment Technology Options XL | Montgomery Investment Technology QuoteTools | Montgomery Investment Technology Risk XL | Montgomery Investment Technology SigTools | Montgomery Investment Technology Utility XL | Moody's KMV CreditEdge | Moody's RiskCalc | Moss Adams Profit Mentor | نرم‌افزار تحلیل صندوق‌های سرمایه‌گذاری مشترک | NetSuite ERP | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions Trading Solutions | NeuroSolutions for MatLab | OptionVue Options Analysis | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Essbase | Oracle Fusion Applications | Oracle Hyperion | Oracle Hyperion Financial Management | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Palisade Bond @nalyst | Palisade Evolver | Palisade StatTools | نرم‌افزار تشخیص الگو | Peer-to-Peer Financial Analysis | نرم‌افزار Perforce Helix | Pi Blue OptWorks Excel | نرم‌افزار مدیریت پورتفولیو | نرم‌افزار قیمت‌گذاری | Qlik Tech QlikView | Quantifying marketability discount QMD modeling software | R | نرم‌افزار تولید گزارش | نرم‌افزار گزارش‌دهی | RiskMetrics Group WealthBench | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SSA Global Infinium Financial Management | Sage 50 Accounting | نرم‌افزار Salesforce | نرم‌افزار تحلیل اوراق بهادار | Spreadware Business Financial Analysis | Spreadware Business Valuator | Spreadware Pro Forma | StataCorp Stata | Steele Mutual Fund and Variable Annuity Expert | زبان پرس‌وجوی ساختاریافته SQL | SunGard BancWare | SunGard Kiodex Risk Workbench | Tableau | نرم‌افزار مالیاتی | TechHackers Convertible Bond @nalyst | TechHackers Credit @nalyst | TechHackers Exotic @nalyst | TechHackers Financial @nalyst | TechHackers IRO @nalyst | TechHackers MBS @nalyst | TechHackers Swap @nalyst | Teradata Database | Tetrahex Fractal Finance | The MathWorks MATLAB | TickQuest NeoTicker | Tips Standard Securities Calculation Bond Analytics Module | Tips Standard Securities Calculation Mortgage-Backed Analytics Module | TradeTools Financial Market Databases | TradeTools Monthly U.S. Economic Database | Trendsetter Software ProAnalyst | Unlimited Learning Resources Valusource Pro | ValuSource BIZCOMPS | Ward Systems Group GeneHunter | Ward Systems Group NeuralShell Predictor | Ward Systems Group NeuroShell Trader | نرم‌افزار مرورگر وب | Whitebirch Software Projected Financials | Wolfram Research Derivatives | Wolfram Research Mathematica | Wolfram Research Mathematica Finance Essentials | Wolfram Research Mathematica UnRisk Pricing Engine | نرم‌افزار Workday | نرم‌افزار Yardi | dailyVest Investment Personalization Platform</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتن | صحبت کردن | گوش دادن فعال | علوم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | کامپیوتر و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمان | تجسم | حافظه | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سر و کار داشتن با مشتریان خارجی یا عموم مردم | سطح رقابت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان کارگزاری | تحلیلگران هوش تجاری | تحلیلگران اعتبار | مشاوران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | مدیران صندوق‌های سرمایه‌گذاری | مسئولان وام | تحلیلگران مدیریت | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مشاوران مالی شخصی | دلالان املاک | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | کارمندان کارگزاری | تحلیلگران هوش تجاری | تحلیلگران اعتبار | مشاوران اعتبار | اقتصاددانان | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | متخصصان ریسک مالی | مدیران صندوق سرمایه‌گذاری | مسئولان وام | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مشاوران مالی شخصی | کارگزاران املاک | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Personal Financial Advisors (مشاوران مالی شخصی)</t>
+          <t>مشاوران مالی شخصی (Personal Financial Advisors)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Certified Financial Planner (CFP) | Financial Advisor | Financial Consultant | Financial Counselor | Financial Life Planner | Financial Planner | Investment Advisor | Portfolio Manager | Wealth Advisor | Wealth Manager</t>
+          <t>برنامه‌ریز مالی دارای گواهی صلاحیت (CFP) | مشاور مالی | مشاور مالی | مشاور مالی | برنامه‌ریز مالی زندگی | برنامه‌ریز مالی | مشاور سرمایه‌گذاری | مدیر پورتفوی | مشاور مدیریت ثروت | مدیر ثروت</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ACT! ACT4Advisors | ASI Client Acquisition Solution | Advent Axys | AdviceAmerica AdvisorVision | Advisory World ICE | نرم‌افزار تخصیص دارایی | Automatic Data Processing ProxyEdge | Brentmark Stock Option Risk Analyzer | Cabinet NG CNG-SAFE | Cheshire Financial Planning Suite | ComplianceMAX | Corel QuattroPro | Cygnus IncomeMax | DataViz Beyond Contacts | EISI NaviPlan | EZ-Data Client Data System | نرم‌افزار برنامه‌ریزی آموزشی | Estate Capitol Needs Analysis | نرم‌افزار برنامه‌ریزی املاک | ExpenseWatch | FileMaker Pro | Finance Logix Education Planner | Finance Logix Insurance Planner | Finance Logix Retirement Planner | Financeware AASim | Financeware Finance File Manager | Financeware WealthSimulator | Financial Planning Consultants Practice Builder | Financial Profiles Profiles+ Professional | نرم‌افزار ارائه برنامه‌ریزی مالی | نرم‌افزار برنامه‌ریزی مالی | نرم‌افزار تولید گزارش مالی | نرم‌افزار حسابداری صندوق | نرم‌افزار Getting Things Done GTD | Host Analytics Host Budget | IBM Domino | IBM Lotus 1-2-3 | IMPACT Wealth Distribution Analysis | Ibbotson Analyst | Ibbotson Portfolio Strategist | Impact PlanLabX3 | Investigo | نرم‌افزار قالب ارزش‌گذاری سرمایه‌گذاری و کسب‌وکار | نرم‌افزار ردیابی سرمایه‌گذاری | J&amp;L Financial Planner | Junxure CRM Software | MasterPlan | Microsoft Access | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Excel | Microsoft Money | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Word | MoneyTree Silver Financial Planner (ویژگی تحلیل مالی) | MoneyTree Silver Financial Planner (ویژگی ارائه) | نرم‌افزار شبیه‌سازی مونت کارلو | Morningstar Principia | نرم‌افزار تحلیل نیازها | Net Worth Strategies Stock Opter Pro | Optima IAS | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle PeopleSoft Financials | PIE Technologies MoneyGuidePro | Pimlico Software DateBk | PlanPlus Pro | PlanScan Portfolio Pathfinder | نرم‌افزار مدیریت پورتفولیو | نرم‌افزار مدیریت تمرین PMS | ProTracker Advantage | Quicken | Redtail Technology Our Business Online | نرم‌افزار برنامه‌ریزی بازنشستگی | Sage 50 Accounting | نرم‌افزار Salesforce | Sawhney ExecPlan | ScanSoft PaperPort Pro | ScenarioNow RetireNow | Structured query language SQL | SunGard Frontier | SunGard LockBox | SunGard PlanningStation | SunGard WebPlaid | Swift | نرم‌افزار برنامه‌ریزی مالیاتی | The Omni Group OmniPlan | Thomson ONE Advisor | Torrid Retirement Planner | Unger Software Methusaleh | WealthTec AllocationPro | WealthTec Foundations | WealthTec WealthMaster | Web Information Solutions Pocket Informant | نرم‌افزار مرورگر وب | World Software Corporation Worldox | eMoneyAdvisor AdvisorPlatform</t>
+          <t>ACT! ACT4Advisors | ASI Client Acquisition Solution | Advent Axys | AdviceAmerica AdvisorVision | Advisory World ICE | نرم‌افزار تخصیص دارایی | Automatic Data Processing ProxyEdge | Brentmark Stock Option Risk Analyzer | Cabinet NG CNG-SAFE | Cheshire Financial Planning Suite | ComplianceMAX | Corel QuattroPro | Cygnus IncomeMax | DataViz Beyond Contacts | EISI NaviPlan | EZ-Data Client Data System | نرم‌افزار برنامه‌ریزی آموزشی | Estate Capitol Needs Analysis | نرم‌افزار برنامه‌ریزی املاک | ExpenseWatch | FileMaker Pro | Finance Logix Education Planner | Finance Logix Insurance Planner | Finance Logix Retirement Planner | Financeware AASim | Financeware Finance File Manager | Financeware WealthSimulator | Financial Planning Consultants Practice Builder | Financial Profiles Profiles+ Professional | نرم‌افزار ارائه برنامه‌ریزی مالی | نرم‌افزار برنامه‌ریزی مالی | نرم‌افزار تولید گزارش مالی | نرم‌افزار حسابداری صندوق | نرم‌افزار Getting Things Done GTD | Host Analytics Host Budget | IBM Domino | IBM Lotus 1-2-3 | IMPACT Wealth Distribution Analysis | Ibbotson Analyst | Ibbotson Portfolio Strategist | Impact PlanLabX3 | Investigo | نرم‌افزار قالب ارزش‌گذاری سرمایه‌گذاری و کسب‌وکار | نرم‌افزار ردیابی سرمایه‌گذاری | J&amp;L Financial Planner | Junxure CRM Software | MasterPlan | Microsoft Access | Microsoft Business Contact Manager | Microsoft Dynamics | Microsoft Excel | Microsoft Money | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Word | MoneyTree Silver Financial Planner (ویژگی تحلیل مالی) | MoneyTree Silver Financial Planner (ویژگی ارائه) | نرم‌افزار شبیه‌سازی مونت کارلو | Morningstar Principia | نرم‌افزار تحلیل نیازها | Net Worth Strategies Stock Opter Pro | Optima IAS | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle PeopleSoft Financials | PIE Technologies MoneyGuidePro | Pimlico Software DateBk | PlanPlus Pro | PlanScan Portfolio Pathfinder | نرم‌افزار مدیریت پورتفولیو | نرم‌افزار مدیریت مطب PMS | ProTracker Advantage | Quicken | Redtail Technology Our Business Online | نرم‌افزار برنامه‌ریزی بازنشستگی | Sage 50 Accounting | نرم‌افزار Salesforce | Sawhney ExecPlan | ScanSoft PaperPort Pro | ScenarioNow RetireNow | زبان پرس‌وجوی ساختاریافته SQL | SunGard Frontier | SunGard LockBox | SunGard PlanningStation | SunGard WebPlaid | Swift | نرم‌افزار برنامه‌ریزی مالیاتی | The Omni Group OmniPlan | Thomson ONE Advisor | Torrid Retirement Planner | Unger Software Methusaleh | WealthTec AllocationPro | WealthTec Foundations | WealthTec WealthMaster | Web Information Solutions Pocket Informant | نرم‌افزار مرورگر وب | World Software Corporation Worldox | eMoneyAdvisor AdvisorPlatform</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | نوشتن | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | وضوح گفتار | استدلال استقرایی | دید نزدیک | بیان نوشتاری | استدلال قیاسی | توانایی عددی | تشخیص گفتار | حساسیت به مسئله | استدلال ریاضی | سازماندهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | خلاقیت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | توانایی عددی | تشخیص گفتار | حساسیت به مسئله | استدلال ریاضی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های رودررو با افراد و درون تیم‌ها | تکرار تصمیم‌گیری | آزادی در تصمیم‌گیری | تماس با دیگران | سر و کار داشتن با مشتریان خارجی یا عموم مردم | فشار زمانی | سطح رقابت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | مکالمات تلفنی | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | سطح رقابت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | تحلیلگران مدیریت | کارمندان حساب‌های جدید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تهیه‌کنندگان مالیات | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | کارمندان کارگزاری | تحلیلگران بودجه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مدیران صندوق سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تهیه‌کنندگان اظهارنامه مالیاتی | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Insurance Underwriters (بیمه‌گران)</t>
+          <t>بیمه‌گران (Insurance Underwriters)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Account Underwriter | Automobile and Property Underwriter | Commercial Lines Underwriter | Health Underwriter | Life Underwriter | Personal Lines Underwriter | Underwriter | Underwriting Consultant</t>
+          <t>ارزیاب ریسک حساب بیمه | ارزیاب ریسک بیمه خودرو و اموال | ارزیاب ریسک بیمه‌های تجاری | ارزیاب ریسک بیمه درمان | ارزیاب ریسک بیمه عمر | ارزیاب ریسک بیمه‌های اشخاص | ارزیاب ریسک بیمه | مشاور ارزیابی ریسک بیمه</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | صحبت کردن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | دید نزدیک | تشخیص گفتار | سازماندهی اطلاعات | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | محیط داخلی، دارای کنترل محیطی | تماس با دیگران | بحث‌های رودررو با افراد و درون تیم‌ها | تکرار تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | سر و کار داشتن با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | موقعیت‌های تعارض</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | اکچوئرها | ارزیابان و ممیزان املاک | کارمندان کارگزاری | تنظیم‌کنندگان، بررسی‌کنندگان و بازپرسان خسارت | تحلیلگران اعتبار | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش ادعاها و سیاست‌های بیمه | نمایندگان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان عنوان، چک‌کنندگان و جستجوگران</t>
+          <t>حسابداران و حسابرسان | کارشناسان آمار بیمه (اکچوئری) | ارزیابان و ممیزان املاک | کارمندان کارگزاری | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | مدیران صندوق سرمایه‌گذاری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0010_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0010_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | فروش و بازاریابی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | مدیریت و امور اداری | رایانه و الکترونیک | امور اداری و دفتری | ریاضیات | اقتصاد و حسابداری | تولید و پردازش</t>
+          <t>زبان انگلیسی | فروش و بازاریابی | خدمات مشتری و شخصی | ارتباطات و رسانه | مدیریت و اداره | رایانه و الکترونیک | اداری | ریاضیات | اقتصاد و حسابداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال قیاسی | درک شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | محاسبات عددی</t>
+          <t>درک کتبی | حساسیت به مسئله | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | درک شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | مدیران تبلیغات و تشویق فروش | متصدیان معاملات اوراق بهادار | تحلیل‌گران هوش تجاری | متصدیان باجه و کرایه کالا | کارشناسان خدمات پس از فروش و امور مشتریان | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | متصدیان ثبت سفارش | کارشناسان خرید (به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی) | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده‌فروشی و تولیدی (به‌جز محصولات علمی و فنی) | کارشناسان فروش فنی و علمی عمده‌فروشی و تولیدی | کارشناسان ارشد راهبرد بازاریابی موتورهای جستجو | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | بازاریابان تلفنی | خریداران عمده و خرده‌فروشی (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران هوش تجاری | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | متصدیان ثبت و پیگیری سفارش‌ها | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | پرسنلی و منابع انسانی | آموزش و تدریس | مهندسی و فناوری | روان‌شناسی | طراحی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | پرسنل و منابع انسانی | آموزش و پرورش | مهندسی و فناوری | روان‌شناسی | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در ادراک | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | تشخیص گفتار | توجه انتخابی | دید دور | تجسم فضایی | سرعت ادراک</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | تشخیص گفتار | توجه انتخابی | بینایی دور | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران انطباق و نظارت قانونی | تحلیل‌گران سیستم‌های رایانه‌ای | مهندسان و معماران سیستم‌های رایانه‌ای | مدیران سیستم‌های اطلاعاتی و رایانه‌ای (فاوا) | بازرسان ساختمانی و ابنیه | تحلیل‌گران جرم‌یابی دیجیتال | مدیران مدیریت بحران و فوریت‌ها | مهندسان حفاظت و ایمنی در برابر حریق | سرپرستان رده‌اول نیروهای حراست و انتظامات | بازرسان و مأموران نظارت بر اماکن خاص | مهندسان بهداشت حرفه‌ای و ایمنی کار | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعات و امنیت | تحلیل‌گران مدیریت و بهبود فرایندها | مدیران شبکه و سیستم‌های رایانه‌ای | کارشناسان آزمون نفوذپذیری | کارشناسان پیشگیری از سرقت و کسری کالا | مدیران حراست و امنیت | نصابان سیستم‌های اعلام حریق و دزدگیر</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | بازرسان ساخت‌وساز و ساختمان | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | مدیران مدیریت بحران و پدافند غیرعامل | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | مدیران حراست و انتظامات | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | امور اداری و دفتری | رایانه و الکترونیک</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | دید نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری در ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان صدور فاکتور و ثبت اسناد | کارمندان حسابداری، دفاتر مالی و حسابرسی | متصدیان معاملات اوراق بهادار | تحلیل‌گران بودجه | متخصصان جبران خدمات، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات | کارشناسان بررسی و تصویب اعتبار | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول کارکنان اداری و دفتری | تحلیل‌گران مدیریت و بهبود فرایندها | متصدیان محاسبات حقوق و دستمزد | مشاوران مالی فردی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | دستیاران آمار | ممیزان، وصول‌کنندگان و مأموران مالیاتی | تنظیم‌کنندگان اظهارنامه‌های مالیاتی | مدیران خزانه‌داری و کنترلرهای مالی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران بودجه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | بازرسان و ارزیابان مالی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | دستیاران و تکنسین‌های آمار | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | شنیدن فعال | سخن گفتن | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | گوش دادن فعال | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اداری | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | حساسیت به مسئله | استدلال ریاضی | محاسبات عددی | دید دور | تشخیص تفاوت رنگ‌ها | توجه انتخابی</t>
+          <t>درک شفاهی | بینایی نزدیک | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | بینایی دور | تشخیص رنگ بصری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان ارزیابی و ممیزی املاک و مستغلات | متصدیان معاملات اوراق بهادار | کارشناسان متره و برآورد هزینه | تحلیل‌گران اعتبارات | کارشناسان بررسی و تصویب اعتبار | بازرسان و محققان اموال دولتی | کارشناسان ارزیابی خسارت بیمه خودرو | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | متصدیان مصاحبه و ثبت پرونده وام | کارشناسان تسهیلات و اعتبارات | کارمندان تدارکات و کارپردازی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید (به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی) | دلالان و کارگزاران املاک | مشاوران و کارشناسان فروش املاک | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | ممیزان، وصول‌کنندگان و مأموران مالیاتی | کارشناسان بررسی و جستجوی اسناد مالکیت | خریداران عمده و خرده‌فروشی (به‌جز محصولات کشاورزی)</t>
+          <t>حسابداران و حسابرسان | کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان برآورد هزینه و مترورها | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | بازرسان و ممیزان اموال دولتی | کارشناسان ارزیابی خسارت خودرو در شرکت‌های بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | کارمندان تدارکات و کارپردازی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید و امور قراردادها | کارگزاران و مدیران معاملات املاک | مشاوران و کارشناسان فروش املاک | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ریاضیات | ساختمان و احداث ابنیه | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | جغرافیا</t>
+          <t>زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص گفتار | درک شفاهی | وضوح گفتار | بیان شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | دید دور | محاسبات عددی | مرتب‌سازی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در ادراک | استدلال ریاضی</t>
+          <t>بینایی نزدیک | تشخیص گفتار | درک شفاهی | وضوح گفتار | بیان شفاهی | درک کتبی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | بینایی دور | توانایی عددی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | بازرسان ساختمانی و ابنیه | کارشناسان متره و برآورد هزینه | تحلیل‌گران اعتبارات | کارشناسان بررسی و تصویب اعتبار | تحلیل‌گران مالی و سرمایه‌گذاری | بازرسان و محققان اموال دولتی | کارشناسان ارزیابی خسارت بیمه خودرو | متصدیان مصاحبه و ثبت پرونده وام | کارشناسان تسهیلات و اعتبارات | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید (به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی) | دلالان و کارگزاران املاک | مشاوران و کارشناسان فروش املاک | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | نقشه‌برداران | ممیزان، وصول‌کنندگان و مأموران مالیاتی | تنظیم‌کنندگان اظهارنامه‌های مالیاتی | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>حسابداران و حسابرسان | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | تحلیل‌گران مالی و سرمایه‌گذاری | بازرسان و ممیزان اموال دولتی | کارشناسان ارزیابی خسارت خودرو در شرکت‌های بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید و امور قراردادها | کارگزاران و مدیران معاملات املاک | مشاوران و کارشناسان فروش املاک | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | مهندسان نقشه‌برداری | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | محاسبات عددی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | وضوح گفتار | بیان کتبی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | سرعت ادراک | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | توانایی عددی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | بیان کتبی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان حسابداری، دفاتر مالی و حسابرسی | مدیران ارشد اجرایی | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات | کارشناسان پذیرش و بررسی واجدین شرایط در برنامه‌های دولتی | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران جذب سرمایه و تأمین مالی | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت و بهبود فرایندها | متصدیان محاسبات حقوق و دستمزد | مشاوران مالی فردی | کارشناسان مدیریت پروژه | ممیزان، وصول‌کنندگان و مأموران مالیاتی | تنظیم‌کنندگان اظهارنامه‌های مالیاتی | مدیران خزانه‌داری و کنترلرهای مالی</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | مدیران عامل و مدیران ارشد اجرایی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران جذب منابع مالی و حامیان | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | کارشناسان مدیریت پروژه | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | سخن گفتن | شنیدن فعال | ریاضیات | نگارش | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | درک مطلب | سخن گفتن | گوش دادن فعال | ریاضیات | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | حقوق و مقررات دولتی | امور اداری و دفتری</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | محاسبات عددی | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | سرعت ادراک | انعطاف‌پذیری در ادراک</t>
+          <t>بیان شفاهی | درک کتبی | استدلال استقرایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | توانایی عددی | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مأموران وصول مطالبات و اسناد | کارمندان حسابداری، دفاتر مالی و حسابرسی | تحلیل‌گران بودجه | کارشناسان بررسی و تصویب اعتبار | مشاوران اعتباری | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان رسیدگی به خسارات و صدور بیمه‌نامه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | مدیران صندوق‌های سرمایه‌گذاری | متصدیان مصاحبه و ثبت پرونده وام | کارشناسان تسهیلات و اعتبارات | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | ممیزان، وصول‌کنندگان و مأموران مالیاتی | تنظیم‌کنندگان اظهارنامه‌های مالیاتی | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | روش‌های علمی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | توانایی حفظ و یادآوری | استدلال ریاضی | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری در ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | متصدیان معاملات اوراق بهادار | تحلیل‌گران هوش تجاری | تحلیل‌گران اعتبارات | مشاوران اعتباری | اقتصاددانان | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | تحلیل‌گران کمی مالی | کارشناسان ریسک مالی | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تسهیلات و اعتبارات | تحلیل‌گران مدیریت و بهبود فرایندها | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | مشاوران مالی فردی | دلالان و کارگزاران املاک | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران هوش تجاری | تحلیل‌گران اعتبارات و تسهیلات | مشاوران اعتباری و مدیریت بدهی | اقتصاددانان | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | مشاوران مالی فردی | کارگزاران و مدیران معاملات املاک | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | روان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | دید نزدیک | بیان کتبی | استدلال قیاسی | محاسبات عددی | تشخیص گفتار | حساسیت به مسئله | استدلال ریاضی | مرتب‌سازی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | توانایی عددی | تشخیص گفتار | حساسیت به مسئله | استدلال ریاضی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | متصدیان معاملات اوراق بهادار | تحلیل‌گران بودجه | تحلیل‌گران اعتبارات | کارشناسان بررسی و تصویب اعتبار | مشاوران اعتباری | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | متصدیان مصاحبه و ثبت پرونده وام | کارشناسان تسهیلات و اعتبارات | تحلیل‌گران مدیریت و بهبود فرایندها | متصدیان افتتاح حساب | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | تنظیم‌کنندگان اظهارنامه‌های مالیاتی | مدیران خزانه‌داری و کنترلرهای مالی</t>
+          <t>حسابداران و حسابرسان | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران بودجه | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان افتتاح حساب | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | فروش و بازاریابی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در ادراک</t>
+          <t>درک کتبی | بیان کتبی | استدلال استقرایی | بیان شفاهی | استدلال قیاسی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | اکچوئرها و کارشناسان محاسبات فنی بیمه | کارشناسان ارزیابی و ممیزی املاک و مستغلات | متصدیان معاملات اوراق بهادار | ارزیابان، کارشناسان و محققان خسارت بیمه | تحلیل‌گران اعتبارات | کارشناسان بررسی و تصویب اعتبار | مشاوران اعتباری | کارشناسان ممیزی مالیاتی و ناظران مالی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان رسیدگی به خسارات و صدور بیمه‌نامه | کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | متصدیان مصاحبه و ثبت پرونده وام | کارشناسان تسهیلات و اعتبارات | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>حسابداران و حسابرسان | اکچوئرها و کارشناسان محاسبات فنی بیمه | کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
